--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -1612,7 +1612,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H16" s="5" t="n">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1876,7 +1876,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-12</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-22</t>
         </is>
       </c>
       <c r="H20" s="5" t="n">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>2026-05-03</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -2140,7 +2140,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>2026-05-19</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-21</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
@@ -2272,7 +2272,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-03-21</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2890,7 +2890,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -3022,7 +3022,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -3154,7 +3154,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -3220,7 +3220,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -3484,7 +3484,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -3550,7 +3550,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -3616,7 +3616,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>2026-04-26</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>2026-04-23</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -3946,7 +3946,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>2026-04-16</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -4012,7 +4012,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -4078,7 +4078,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-14</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -4408,7 +4408,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-04-28</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -4474,7 +4474,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-14</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -4540,7 +4540,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -4606,7 +4606,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-08</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>2026-04-08</t>
+          <t>2026-04-09</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -4870,7 +4870,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -5068,7 +5068,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -5332,7 +5332,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -5530,7 +5530,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -5728,7 +5728,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -5860,7 +5860,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -5926,7 +5926,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -5992,7 +5992,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -6124,7 +6124,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -6190,7 +6190,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -6322,7 +6322,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -6388,7 +6388,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="G88" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H88" s="5" t="n">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="G89" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H89" s="5" t="n">
@@ -6586,7 +6586,7 @@
       </c>
       <c r="G90" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H90" s="5" t="n">
@@ -6652,7 +6652,7 @@
       </c>
       <c r="G91" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H91" s="5" t="n">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="G92" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H92" s="5" t="n">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="G93" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H93" s="5" t="n">
@@ -6850,7 +6850,7 @@
       </c>
       <c r="G94" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H94" s="5" t="n">
@@ -6916,7 +6916,7 @@
       </c>
       <c r="G95" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H95" s="5" t="n">
@@ -6982,7 +6982,7 @@
       </c>
       <c r="G96" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H96" s="5" t="n">
@@ -7048,7 +7048,7 @@
       </c>
       <c r="G97" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H97" s="5" t="n">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="G98" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H98" s="5" t="n">
@@ -7180,7 +7180,7 @@
       </c>
       <c r="G99" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H99" s="5" t="n">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="G100" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H100" s="5" t="n">
@@ -7312,7 +7312,7 @@
       </c>
       <c r="G101" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H101" s="5" t="n">
@@ -7378,7 +7378,7 @@
       </c>
       <c r="G102" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H102" s="5" t="n">
@@ -7444,7 +7444,7 @@
       </c>
       <c r="G103" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H103" s="5" t="n">
@@ -7510,7 +7510,7 @@
       </c>
       <c r="G104" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H104" s="5" t="n">
@@ -7576,7 +7576,7 @@
       </c>
       <c r="G105" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H105" s="5" t="n">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="G106" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H106" s="5" t="n">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="G107" s="3" t="inlineStr">
         <is>
-          <t>2026-03-29</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="H107" s="5" t="n">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="G108" s="3" t="inlineStr">
         <is>
-          <t>2026-03-26</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="H108" s="5" t="n">
@@ -7840,7 +7840,7 @@
       </c>
       <c r="G109" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H109" s="5" t="n">
@@ -7906,7 +7906,7 @@
       </c>
       <c r="G110" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H110" s="5" t="n">
@@ -7972,7 +7972,7 @@
       </c>
       <c r="G111" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H111" s="5" t="n">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="G112" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H112" s="5" t="n">
@@ -8104,7 +8104,7 @@
       </c>
       <c r="G113" s="3" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H113" s="5" t="n">
@@ -8170,7 +8170,7 @@
       </c>
       <c r="G114" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H114" s="5" t="n">
@@ -8236,7 +8236,7 @@
       </c>
       <c r="G115" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H115" s="5" t="n">
@@ -8302,7 +8302,7 @@
       </c>
       <c r="G116" s="3" t="inlineStr">
         <is>
-          <t>2026-03-25</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H116" s="5" t="n">
@@ -8368,7 +8368,7 @@
       </c>
       <c r="G117" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H117" s="5" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="G118" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H118" s="5" t="n">
@@ -8500,7 +8500,7 @@
       </c>
       <c r="G119" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H119" s="5" t="n">
@@ -8566,7 +8566,7 @@
       </c>
       <c r="G120" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H120" s="5" t="n">
@@ -8632,7 +8632,7 @@
       </c>
       <c r="G121" s="3" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>2026-03-25</t>
         </is>
       </c>
       <c r="H121" s="5" t="n">
@@ -8768,7 +8768,7 @@
       </c>
       <c r="G123" s="3" t="inlineStr">
         <is>
-          <t>2026-04-14</t>
+          <t>2026-04-15</t>
         </is>
       </c>
       <c r="H123" s="5" t="n">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="G124" s="3" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H124" s="5" t="n">
@@ -8900,7 +8900,7 @@
       </c>
       <c r="G125" s="3" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-04-01</t>
         </is>
       </c>
       <c r="H125" s="5" t="n">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="G126" s="3" t="inlineStr">
         <is>
-          <t>2026-03-19</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="H126" s="5" t="n">
@@ -9333,7 +9333,7 @@
           <t>A | 287呎 (1房)
 $1016万
 $35,401/呎
-(26年-05月-11日)</t>
+(26年-05月-12日)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
@@ -9341,7 +9341,7 @@
           <t>B | 284呎 (1房)
 $1026万
 $36,144/呎
-(26年-07月-07日)</t>
+(26年-07月-08日)</t>
         </is>
       </c>
       <c r="D8" s="22" t="inlineStr">
@@ -9349,7 +9349,7 @@
           <t>C | 284呎 (1房)
 $1028万
 $36,215/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="E8" s="22" t="inlineStr">
@@ -9357,7 +9357,7 @@
           <t>D | 325呎 (1房)
 $1153万
 $35,477/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F8" s="22" t="inlineStr">
@@ -9365,7 +9365,7 @@
           <t>E | 412呎 (2房)
 $1425万
 $34,587/呎
-(26年-05月-10日)</t>
+(26年-05月-11日)</t>
         </is>
       </c>
       <c r="G8" s="23" t="inlineStr">
@@ -9388,7 +9388,7 @@
           <t>A | 287呎 (1房)
 $994万
 $34,627/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -9396,7 +9396,7 @@
           <t>B | 284呎 (1房)
 $1011万
 $35,595/呎
-(26年-04月-20日)</t>
+(26年-04月-21日)</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -9404,7 +9404,7 @@
           <t>C | 284呎 (1房)
 $1013万
 $35,665/呎
-(26年-05月-19日)</t>
+(26年-05月-20日)</t>
         </is>
       </c>
       <c r="E9" s="22" t="inlineStr">
@@ -9412,7 +9412,7 @@
           <t>D | 325呎 (1房)
 $1139万
 $35,040/呎
-(26年-05月-06日)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F9" s="22" t="inlineStr">
@@ -9420,7 +9420,7 @@
           <t>E | 412呎 (2房)
 $1410万
 $34,223/呎
-(26年-05月-03日)</t>
+(26年-05月-04日)</t>
         </is>
       </c>
       <c r="G9" s="22" t="inlineStr">
@@ -9428,7 +9428,7 @@
           <t>F | 288呎 (1房)
 $993万
 $34,479/呎
-(26年-05月-21日)</t>
+(26年-05月-22日)</t>
         </is>
       </c>
     </row>
@@ -9498,7 +9498,7 @@
           <t>A | 287呎 (1房)
 $953万
 $33,206/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -9506,7 +9506,7 @@
           <t>B | 284呎 (1房)
 $977万
 $34,398/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="D11" s="22" t="inlineStr">
@@ -9514,7 +9514,7 @@
           <t>C | 284呎 (1房)
 $980万
 $34,507/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="E11" s="22" t="inlineStr">
@@ -9522,7 +9522,7 @@
           <t>D | 325呎 (1房)
 $1110万
 $34,154/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="F11" s="22" t="inlineStr">
@@ -9530,7 +9530,7 @@
           <t>E | 412呎 (2房)
 $1376万
 $33,400/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G11" s="22" t="inlineStr">
@@ -9538,7 +9538,7 @@
           <t>F | 288呎 (1房)
 $915万
 $31,771/呎
-(26年-03月-20日)</t>
+(26年-03月-21日)</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
           <t>A | 287呎 (1房)
 $924万
 $32,181/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -9561,7 +9561,7 @@
           <t>B | 284呎 (1房)
 $946万
 $33,327/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="D12" s="22" t="inlineStr">
@@ -9569,7 +9569,7 @@
           <t>C | 284呎 (1房)
 $948万
 $33,373/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="E12" s="22" t="inlineStr">
@@ -9577,7 +9577,7 @@
           <t>D | 325呎 (1房)
 $1076万
 $33,108/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="F12" s="22" t="inlineStr">
@@ -9585,7 +9585,7 @@
           <t>E | 412呎 (2房)
 $1333万
 $32,354/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="G12" s="22" t="inlineStr">
@@ -9593,7 +9593,7 @@
           <t>F | 288呎 (1房)
 $896万
 $31,111/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
     </row>
@@ -9608,7 +9608,7 @@
           <t>A | 287呎 (1房)
 $916万
 $31,923/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -9616,7 +9616,7 @@
           <t>B | 284呎 (1房)
 $937万
 $33,000/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -9624,7 +9624,7 @@
           <t>C | 284呎 (1房)
 $940万
 $33,081/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="E13" s="22" t="inlineStr">
@@ -9632,7 +9632,7 @@
           <t>D | 325呎 (1房)
 $1078万
 $33,169/呎
-(26年-04月-23日)</t>
+(26年-04月-24日)</t>
         </is>
       </c>
       <c r="F13" s="22" t="inlineStr">
@@ -9640,7 +9640,7 @@
           <t>E | 412呎 (2房)
 $1322万
 $32,095/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
       <c r="G13" s="22" t="inlineStr">
@@ -9648,7 +9648,7 @@
           <t>F | 288呎 (1房)
 $898万
 $31,181/呎
-(26年-04月-26日)</t>
+(26年-04月-27日)</t>
         </is>
       </c>
     </row>
@@ -9663,7 +9663,7 @@
           <t>A | 287呎 (1房)
 $903万
 $31,470/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="C14" s="22" t="inlineStr">
@@ -9671,7 +9671,7 @@
           <t>B | 284呎 (1房)
 $927万
 $32,637/呎
-(26年-04月-12日)</t>
+(26年-04月-13日)</t>
         </is>
       </c>
       <c r="D14" s="22" t="inlineStr">
@@ -9679,7 +9679,7 @@
           <t>C | 284呎 (1房)
 $929万
 $32,701/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E14" s="22" t="inlineStr">
@@ -9687,7 +9687,7 @@
           <t>D | 325呎 (1房)
 $1056万
 $32,477/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="F14" s="22" t="inlineStr">
@@ -9695,7 +9695,7 @@
           <t>E | 412呎 (2房)
 $1307万
 $31,728/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G14" s="22" t="inlineStr">
@@ -9703,7 +9703,7 @@
           <t>F | 288呎 (1房)
 $868万
 $30,139/呎
-(26年-04月-16日)</t>
+(26年-04月-17日)</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
           <t>A | 287呎 (1房)
 $898万
 $31,300/呎
-(26年-04月-08日)</t>
+(26年-04月-09日)</t>
         </is>
       </c>
       <c r="C15" s="22" t="inlineStr">
@@ -9726,7 +9726,7 @@
           <t>B | 284呎 (1房)
 $918万
 $32,324/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="D15" s="22" t="inlineStr">
@@ -9734,7 +9734,7 @@
           <t>C | 284呎 (1房)
 $920万
 $32,377/呎
-(26年-04月-07日)</t>
+(26年-04月-08日)</t>
         </is>
       </c>
       <c r="E15" s="22" t="inlineStr">
@@ -9742,7 +9742,7 @@
           <t>D | 325呎 (1房)
 $1045万
 $32,154/呎
-(26年-04月-13日)</t>
+(26年-04月-14日)</t>
         </is>
       </c>
       <c r="F15" s="22" t="inlineStr">
@@ -9750,7 +9750,7 @@
           <t>E | 412呎 (2房)
 $1294万
 $31,415/呎
-(26年-04月-27日)</t>
+(26年-04月-28日)</t>
         </is>
       </c>
       <c r="G15" s="22" t="inlineStr">
@@ -9758,7 +9758,7 @@
           <t>F | 288呎 (1房)
 $860万
 $29,858/呎
-(26年-03月-13日)</t>
+(26年-03月-14日)</t>
         </is>
       </c>
     </row>
@@ -9773,7 +9773,7 @@
           <t>A | 287呎 (1房)
 $868万
 $30,244/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="C16" s="22" t="inlineStr">
@@ -9781,7 +9781,7 @@
           <t>B | 284呎 (1房)
 $888万
 $31,268/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D16" s="22" t="inlineStr">
@@ -9789,7 +9789,7 @@
           <t>C | 284呎 (1房)
 $891万
 $31,359/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E16" s="22" t="inlineStr">
@@ -9797,7 +9797,7 @@
           <t>D | 325呎 (1房)
 $1023万
 $31,477/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F16" s="22" t="inlineStr">
@@ -9805,7 +9805,7 @@
           <t>E | 412呎 (2房)
 $1253万
 $30,408/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="G16" s="22" t="inlineStr">
@@ -9813,7 +9813,7 @@
           <t>F | 288呎 (1房)
 $834万
 $28,951/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
     </row>
@@ -9828,7 +9828,7 @@
           <t>A | 287呎 (1房)
 $812万
 $28,310/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="C17" s="22" t="inlineStr">
@@ -9836,7 +9836,7 @@
           <t>B | 284呎 (1房)
 $832万
 $29,296/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="D17" s="22" t="inlineStr">
@@ -9844,7 +9844,7 @@
           <t>C | 284呎 (1房)
 $834万
 $29,352/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E17" s="22" t="inlineStr">
@@ -9852,7 +9852,7 @@
           <t>D | 325呎 (1房)
 $947万
 $29,129/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F17" s="22" t="inlineStr">
@@ -9860,7 +9860,7 @@
           <t>E | 412呎 (2房)
 $1173万
 $28,464/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G17" s="22" t="inlineStr">
@@ -9868,7 +9868,7 @@
           <t>F | 288呎 (1房)
 $780万
 $27,101/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -9883,7 +9883,7 @@
           <t>A | 287呎 (1房)
 $804万
 $28,000/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="C18" s="22" t="inlineStr">
@@ -9891,7 +9891,7 @@
           <t>B | 284呎 (1房)
 $823万
 $28,972/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="D18" s="22" t="inlineStr">
@@ -9899,7 +9899,7 @@
           <t>C | 284呎 (1房)
 $824万
 $29,028/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="E18" s="22" t="inlineStr">
@@ -9907,7 +9907,7 @@
           <t>D | 325呎 (1房)
 $936万
 $28,806/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="F18" s="22" t="inlineStr">
@@ -9915,7 +9915,7 @@
           <t>E | 412呎 (2房)
 $1160万
 $28,148/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
       <c r="G18" s="22" t="inlineStr">
@@ -9923,7 +9923,7 @@
           <t>F | 288呎 (1房)
 $772万
 $26,802/呎
-(26年-04月-01日)</t>
+(26年-04月-02日)</t>
         </is>
       </c>
     </row>
@@ -9938,7 +9938,7 @@
           <t>A | 287呎 (1房)
 $821万
 $28,596/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C19" s="22" t="inlineStr">
@@ -9946,7 +9946,7 @@
           <t>B | 284呎 (1房)
 $843万
 $29,683/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D19" s="22" t="inlineStr">
@@ -9954,7 +9954,7 @@
           <t>C | 284呎 (1房)
 $845万
 $29,754/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E19" s="22" t="inlineStr">
@@ -9962,7 +9962,7 @@
           <t>D | 325呎 (1房)
 $956万
 $29,422/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F19" s="22" t="inlineStr">
@@ -9970,7 +9970,7 @@
           <t>E | 412呎 (2房)
 $1184万
 $28,750/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G19" s="22" t="inlineStr">
@@ -9978,7 +9978,7 @@
           <t>F | 288呎 (1房)
 $788万
 $27,375/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
           <t>A | 287呎 (1房)
 $786万
 $27,401/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="C20" s="22" t="inlineStr">
@@ -10001,7 +10001,7 @@
           <t>B | 284呎 (1房)
 $805万
 $28,352/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D20" s="22" t="inlineStr">
@@ -10009,7 +10009,7 @@
           <t>C | 284呎 (1房)
 $807万
 $28,408/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="E20" s="22" t="inlineStr">
@@ -10017,7 +10017,7 @@
           <t>D | 325呎 (1房)
 $916万
 $28,191/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F20" s="22" t="inlineStr">
@@ -10025,7 +10025,7 @@
           <t>E | 412呎 (2房)
 $1135万
 $27,546/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="G20" s="22" t="inlineStr">
@@ -10033,7 +10033,7 @@
           <t>F | 288呎 (1房)
 $755万
 $26,229/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
     </row>
@@ -10048,7 +10048,7 @@
           <t>A | 287呎 (1房)
 $778万
 $27,115/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="C21" s="22" t="inlineStr">
@@ -10056,7 +10056,7 @@
           <t>B | 284呎 (1房)
 $797万
 $28,060/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="D21" s="22" t="inlineStr">
@@ -10064,7 +10064,7 @@
           <t>C | 284呎 (1房)
 $798万
 $28,113/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="E21" s="22" t="inlineStr">
@@ -10072,7 +10072,7 @@
           <t>D | 325呎 (1房)
 $907万
 $27,898/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F21" s="22" t="inlineStr">
@@ -10080,7 +10080,7 @@
           <t>E | 412呎 (2房)
 $1123万
 $27,262/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="G21" s="22" t="inlineStr">
@@ -10088,7 +10088,7 @@
           <t>F | 288呎 (1房)
 $748万
 $25,958/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
     </row>
@@ -10103,7 +10103,7 @@
           <t>A | 287呎 (1房)
 $769万
 $26,805/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="C22" s="22" t="inlineStr">
@@ -10111,7 +10111,7 @@
           <t>B | 284呎 (1房)
 $788万
 $27,732/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="D22" s="22" t="inlineStr">
@@ -10119,7 +10119,7 @@
           <t>C | 284呎 (1房)
 $789万
 $27,792/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="E22" s="22" t="inlineStr">
@@ -10127,7 +10127,7 @@
           <t>D | 325呎 (1房)
 $896万
 $27,578/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F22" s="22" t="inlineStr">
@@ -10135,7 +10135,7 @@
           <t>E | 412呎 (2房)
 $1110万
 $26,947/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="G22" s="22" t="inlineStr">
@@ -10143,7 +10143,7 @@
           <t>F | 288呎 (1房)
 $739万
 $25,656/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -10158,7 +10158,7 @@
           <t>A | 287呎 (1房)
 $761万
 $26,519/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="C23" s="22" t="inlineStr">
@@ -10166,7 +10166,7 @@
           <t>B | 284呎 (1房)
 $779万
 $27,440/呎
-(26年-03月-26日)</t>
+(26年-03月-27日)</t>
         </is>
       </c>
       <c r="D23" s="22" t="inlineStr">
@@ -10174,7 +10174,7 @@
           <t>C | 284呎 (1房)
 $781万
 $27,496/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="E23" s="22" t="inlineStr">
@@ -10182,7 +10182,7 @@
           <t>D | 325呎 (1房)
 $887万
 $27,283/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="F23" s="22" t="inlineStr">
@@ -10190,7 +10190,7 @@
           <t>E | 412呎 (2房)
 $1098万
 $26,660/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
       <c r="G23" s="22" t="inlineStr">
@@ -10198,7 +10198,7 @@
           <t>F | 288呎 (1房)
 $731万
 $25,385/呎
-(26年-03月-29日)</t>
+(26年-03月-30日)</t>
         </is>
       </c>
     </row>
@@ -10213,7 +10213,7 @@
           <t>A | 287呎 (1房)
 $752万
 $26,206/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="C24" s="22" t="inlineStr">
@@ -10221,7 +10221,7 @@
           <t>B | 284呎 (1房)
 $770万
 $27,116/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="D24" s="22" t="inlineStr">
@@ -10229,7 +10229,7 @@
           <t>C | 284呎 (1房)
 $772万
 $27,169/呎
-(26年-03月-23日)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="E24" s="22" t="inlineStr">
@@ -10237,7 +10237,7 @@
           <t>D | 325呎 (1房)
 $876万
 $26,963/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="F24" s="22" t="inlineStr">
@@ -10245,7 +10245,7 @@
           <t>E | 412呎 (2房)
 $1085万
 $26,345/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G24" s="22" t="inlineStr">
@@ -10253,7 +10253,7 @@
           <t>F | 288呎 (1房)
 $722万
 $25,087/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
           <t>A | 287呎 (1房)
 $744万
 $25,920/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="C25" s="22" t="inlineStr">
@@ -10276,7 +10276,7 @@
           <t>B | 284呎 (1房)
 $762万
 $26,820/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="D25" s="22" t="inlineStr">
@@ -10284,7 +10284,7 @@
           <t>C | 284呎 (1房)
 $763万
 $26,873/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="E25" s="22" t="inlineStr">
@@ -10292,7 +10292,7 @@
           <t>D | 325呎 (1房)
 $867万
 $26,668/呎
-(26年-03月-24日)</t>
+(26年-03月-25日)</t>
         </is>
       </c>
       <c r="F25" s="22" t="inlineStr">
@@ -10300,7 +10300,7 @@
           <t>E | 412呎 (2房)
 $1074万
 $26,061/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="G25" s="22" t="inlineStr">
@@ -10308,7 +10308,7 @@
           <t>F | 288呎 (1房)
 $715万
 $24,812/呎
-(26年-03月-25日)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
     </row>
@@ -10331,7 +10331,7 @@
           <t>B | 286呎 (1房)
 $753万
 $26,339/呎
-(26年-03月-19日)</t>
+(26年-03月-20日)</t>
         </is>
       </c>
       <c r="D26" s="22" t="inlineStr">
@@ -10339,7 +10339,7 @@
           <t>C | 284呎 (1房)
 $755万
 $26,581/呎
-(26年-03月-31日)</t>
+(26年-04月-01日)</t>
         </is>
       </c>
       <c r="E26" s="22" t="inlineStr">
@@ -10347,7 +10347,7 @@
           <t>D | 325呎 (1房)
 $857万
 $26,375/呎
-(26年-03月-30日)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
       <c r="F26" s="22" t="inlineStr">
@@ -10355,7 +10355,7 @@
           <t>E | 374呎 (2房)
 $1350万
 $36,096/呎
-(26年-04月-14日)</t>
+(26年-04月-15日)</t>
         </is>
       </c>
       <c r="G26" s="23" t="inlineStr">

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -126,8 +126,7 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00002060"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -275,7 +274,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1537,7 +1536,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2333,7 +2332,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2403,7 +2402,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2473,7 +2472,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2543,7 +2542,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -2613,7 +2612,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2683,7 +2682,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -8693,7 +8692,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -9027,7 +9026,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已定价未售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9145,12 +9144,12 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>9</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="D3" s="16" t="inlineStr">
@@ -9373,7 +9372,7 @@
           <t>F | 288呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -9443,7 +9442,7 @@
           <t>A | 287呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -9451,7 +9450,7 @@
           <t>B | 284呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -9459,7 +9458,7 @@
           <t>C | 284呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -9467,7 +9466,7 @@
           <t>D | 325呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9475,7 +9474,7 @@
           <t>E | 412呎 (2房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -9483,7 +9482,7 @@
           <t>F | 288呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>
@@ -10323,7 +10322,7 @@
           <t>A | 247呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -10363,7 +10362,7 @@
           <t>F | 251呎 (1房)
 招标单位
 -
-(在售)</t>
+(已定价未售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -126,7 +126,8 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -274,7 +275,7 @@
     <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1536,7 +1537,7 @@
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
@@ -2332,7 +2333,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -2402,7 +2403,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -2472,7 +2473,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -2542,23 +2543,19 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I29" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="n">
+        <v>10450000</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>36796</v>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
@@ -2567,12 +2564,12 @@
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
@@ -2582,7 +2579,7 @@
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2609,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -2682,7 +2679,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -8692,7 +8689,7 @@
       </c>
       <c r="F122" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G122" s="3" t="inlineStr">
@@ -9026,7 +9023,7 @@
       </c>
       <c r="F127" s="3" t="inlineStr">
         <is>
-          <t>已定价未售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G127" s="3" t="inlineStr">
@@ -9144,17 +9141,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9372,7 +9369,7 @@
           <t>F | 288呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9439,7 @@
           <t>A | 287呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -9450,15 +9447,15 @@
           <t>B | 284呎 (1房)
 招标单位
 -
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
+(在售)</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
-招标单位
--
-(已定价未售)</t>
+$1045万
+$36,796/呎
+(26年-08月-08日)</t>
         </is>
       </c>
       <c r="E10" s="23" t="inlineStr">
@@ -9466,7 +9463,7 @@
           <t>D | 325呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="F10" s="23" t="inlineStr">
@@ -9474,7 +9471,7 @@
           <t>E | 412呎 (2房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">
@@ -9482,7 +9479,7 @@
           <t>F | 288呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>
@@ -10322,7 +10319,7 @@
           <t>A | 247呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="C26" s="22" t="inlineStr">
@@ -10362,7 +10359,7 @@
           <t>F | 251呎 (1房)
 招标单位
 -
-(已定价未售)</t>
+(在售)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -2403,23 +2403,19 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="n">
+        <v>14520000</v>
+      </c>
+      <c r="I27" s="5" t="n">
+        <v>35243</v>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
@@ -2428,12 +2424,12 @@
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -2443,7 +2439,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9137,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9151,7 +9147,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>106</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9466,12 +9462,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
-招标单位
--
-(在售)</t>
+$1452万
+$35,243/呎
+(26年-08月-12日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -4334,7 +4334,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>2026-03-14</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -9750,7 +9750,7 @@
           <t>F | 288呎 (1房)
 $860万
 $29,858/呎
-(26年-03月-14日)</t>
+(26年-08月-14日)</t>
         </is>
       </c>
     </row>

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -2605,23 +2605,19 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H30" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I30" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="n">
+        <v>10419000</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>36687</v>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
@@ -2630,12 +2626,12 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
@@ -2645,7 +2641,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9133,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9147,7 +9143,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9438,12 +9434,12 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
-招标单位
--
-(在售)</t>
+$1042万
+$36,687/呎
+(26年-08月-14日)</t>
         </is>
       </c>
       <c r="D10" s="22" t="inlineStr">

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -2408,7 +2408,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -9463,7 +9463,7 @@
           <t>E | 412呎 (2房)
 $1452万
 $35,243/呎
-(26年-08月-12日)</t>
+(26年-08月-25日)</t>
         </is>
       </c>
       <c r="G10" s="23" t="inlineStr">

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -121,13 +121,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -272,10 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -1212,12 +1212,12 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1257,7 +1257,7 @@
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -1282,12 +1282,12 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
@@ -1407,12 +1407,12 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1422,12 +1422,12 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1467,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>待售</t>
+          <t>在售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
@@ -1477,12 +1477,12 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>招标单位</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>暂无</t>
+          <t>-</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-08-08</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -2671,23 +2671,19 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-27</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="n">
+        <v>10313000</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>35934</v>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
@@ -2696,12 +2692,12 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
@@ -2711,7 +2707,7 @@
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9133,27 +9129,27 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
           <t>6</t>
-        </is>
-      </c>
-      <c r="C3" s="15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D3" s="16" t="inlineStr">
-        <is>
-          <t>108</t>
-        </is>
-      </c>
-      <c r="E3" s="17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" s="18" t="inlineStr">
-        <is>
-          <t>11</t>
         </is>
       </c>
     </row>
@@ -9268,44 +9264,44 @@
           <t>27</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 471呎 (2房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>B | 284呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>B | 284呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="D7" s="22" t="inlineStr">
+        <is>
+          <t>C | 284呎 (1房)
+招标单位
 -
+(在售)</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 328呎 (1房)
+招标单位
 -
-(待售)</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>C | 284呎 (1房)
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="22" t="inlineStr">
+        <is>
+          <t>E | 412呎 (2房)
+招标单位
 -
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="inlineStr">
-        <is>
-          <t>D | 328呎 (1房)
--
--
-(待售)</t>
-        </is>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>E | 412呎 (2房)
--
--
-(待售)</t>
+(在售)</t>
         </is>
       </c>
       <c r="G7" s="21" t="inlineStr"/>
@@ -9316,7 +9312,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $1016万
@@ -9324,7 +9320,7 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $1026万
@@ -9332,7 +9328,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $1028万
@@ -9340,7 +9336,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E8" s="22" t="inlineStr">
+      <c r="E8" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1153万
@@ -9348,7 +9344,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1425万
@@ -9356,7 +9352,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 招标单位
@@ -9371,7 +9367,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $994万
@@ -9379,7 +9375,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $1011万
@@ -9387,7 +9383,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $1013万
@@ -9395,7 +9391,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1139万
@@ -9403,7 +9399,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1410万
@@ -9411,7 +9407,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $993万
@@ -9429,12 +9425,12 @@
       <c r="B10" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+$1031万
+$35,934/呎
+(26年-08月-27日)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $1042万
@@ -9442,15 +9438,15 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $1045万
 $36,796/呎
-(26年-08月-08日)</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="inlineStr">
+(26年-08月-27日)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 招标单位
@@ -9458,7 +9454,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1452万
@@ -9466,7 +9462,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="G10" s="23" t="inlineStr">
+      <c r="G10" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 招标单位
@@ -9481,7 +9477,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $953万
@@ -9489,7 +9485,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $977万
@@ -9497,7 +9493,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $980万
@@ -9505,7 +9501,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1110万
@@ -9513,7 +9509,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1376万
@@ -9521,7 +9517,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="G11" s="22" t="inlineStr">
+      <c r="G11" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $915万
@@ -9536,7 +9532,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $924万
@@ -9544,7 +9540,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $946万
@@ -9552,7 +9548,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $948万
@@ -9560,7 +9556,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1076万
@@ -9568,7 +9564,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1333万
@@ -9576,7 +9572,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="G12" s="22" t="inlineStr">
+      <c r="G12" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $896万
@@ -9591,7 +9587,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $916万
@@ -9599,7 +9595,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $937万
@@ -9607,7 +9603,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $940万
@@ -9615,7 +9611,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1078万
@@ -9623,7 +9619,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="F13" s="22" t="inlineStr">
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1322万
@@ -9631,7 +9627,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="G13" s="22" t="inlineStr">
+      <c r="G13" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $898万
@@ -9646,7 +9642,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $903万
@@ -9654,7 +9650,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $927万
@@ -9662,7 +9658,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $929万
@@ -9670,7 +9666,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="E14" s="22" t="inlineStr">
+      <c r="E14" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1056万
@@ -9678,7 +9674,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="F14" s="22" t="inlineStr">
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1307万
@@ -9686,7 +9682,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="G14" s="22" t="inlineStr">
+      <c r="G14" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $868万
@@ -9701,7 +9697,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B15" s="22" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $898万
@@ -9709,7 +9705,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $918万
@@ -9717,7 +9713,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $920万
@@ -9725,7 +9721,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="E15" s="22" t="inlineStr">
+      <c r="E15" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1045万
@@ -9733,7 +9729,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="F15" s="22" t="inlineStr">
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1294万
@@ -9741,7 +9737,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="G15" s="22" t="inlineStr">
+      <c r="G15" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $860万
@@ -9756,7 +9752,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B16" s="22" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $868万
@@ -9764,7 +9760,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="C16" s="22" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $888万
@@ -9772,7 +9768,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D16" s="22" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $891万
@@ -9780,7 +9776,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="E16" s="22" t="inlineStr">
+      <c r="E16" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1023万
@@ -9788,7 +9784,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="F16" s="22" t="inlineStr">
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1253万
@@ -9796,7 +9792,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="G16" s="22" t="inlineStr">
+      <c r="G16" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $834万
@@ -9811,7 +9807,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $812万
@@ -9819,7 +9815,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $832万
@@ -9827,7 +9823,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $834万
@@ -9835,7 +9831,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="E17" s="22" t="inlineStr">
+      <c r="E17" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $947万
@@ -9843,7 +9839,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1173万
@@ -9851,7 +9847,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="G17" s="22" t="inlineStr">
+      <c r="G17" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $780万
@@ -9866,7 +9862,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $804万
@@ -9874,7 +9870,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $823万
@@ -9882,7 +9878,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $824万
@@ -9890,7 +9886,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="E18" s="22" t="inlineStr">
+      <c r="E18" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $936万
@@ -9898,7 +9894,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="F18" s="22" t="inlineStr">
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1160万
@@ -9906,7 +9902,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="G18" s="22" t="inlineStr">
+      <c r="G18" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $772万
@@ -9921,7 +9917,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $821万
@@ -9929,7 +9925,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $843万
@@ -9937,7 +9933,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $845万
@@ -9945,7 +9941,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="E19" s="22" t="inlineStr">
+      <c r="E19" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $956万
@@ -9953,7 +9949,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F19" s="22" t="inlineStr">
+      <c r="F19" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1184万
@@ -9961,7 +9957,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="G19" s="22" t="inlineStr">
+      <c r="G19" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $788万
@@ -9976,7 +9972,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $786万
@@ -9984,7 +9980,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $805万
@@ -9992,7 +9988,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $807万
@@ -10000,7 +9996,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="E20" s="22" t="inlineStr">
+      <c r="E20" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $916万
@@ -10008,7 +10004,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F20" s="22" t="inlineStr">
+      <c r="F20" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1135万
@@ -10016,7 +10012,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="G20" s="22" t="inlineStr">
+      <c r="G20" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $755万
@@ -10031,7 +10027,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $778万
@@ -10039,7 +10035,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $797万
@@ -10047,7 +10043,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $798万
@@ -10055,7 +10051,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="E21" s="22" t="inlineStr">
+      <c r="E21" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $907万
@@ -10063,7 +10059,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F21" s="22" t="inlineStr">
+      <c r="F21" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1123万
@@ -10071,7 +10067,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="G21" s="22" t="inlineStr">
+      <c r="G21" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $748万
@@ -10086,7 +10082,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $769万
@@ -10094,7 +10090,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $788万
@@ -10102,7 +10098,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $789万
@@ -10110,7 +10106,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="E22" s="22" t="inlineStr">
+      <c r="E22" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $896万
@@ -10118,7 +10114,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="F22" s="22" t="inlineStr">
+      <c r="F22" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1110万
@@ -10126,7 +10122,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="G22" s="22" t="inlineStr">
+      <c r="G22" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $739万
@@ -10141,7 +10137,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $761万
@@ -10149,7 +10145,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $779万
@@ -10157,7 +10153,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $781万
@@ -10165,7 +10161,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="E23" s="22" t="inlineStr">
+      <c r="E23" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $887万
@@ -10173,7 +10169,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="F23" s="22" t="inlineStr">
+      <c r="F23" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1098万
@@ -10181,7 +10177,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="G23" s="22" t="inlineStr">
+      <c r="G23" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $731万
@@ -10196,7 +10192,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $752万
@@ -10204,7 +10200,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $770万
@@ -10212,7 +10208,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $772万
@@ -10220,7 +10216,7 @@
 (26年-03月-24日)</t>
         </is>
       </c>
-      <c r="E24" s="22" t="inlineStr">
+      <c r="E24" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $876万
@@ -10228,7 +10224,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="F24" s="22" t="inlineStr">
+      <c r="F24" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1085万
@@ -10236,7 +10232,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="G24" s="22" t="inlineStr">
+      <c r="G24" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $722万
@@ -10251,7 +10247,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $744万
@@ -10259,7 +10255,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $762万
@@ -10267,7 +10263,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $763万
@@ -10275,7 +10271,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="E25" s="22" t="inlineStr">
+      <c r="E25" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $867万
@@ -10283,7 +10279,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F25" s="22" t="inlineStr">
+      <c r="F25" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1074万
@@ -10291,7 +10287,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="G25" s="22" t="inlineStr">
+      <c r="G25" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $715万
@@ -10306,7 +10302,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="22" t="inlineStr">
         <is>
           <t>A | 247呎 (1房)
 招标单位
@@ -10314,7 +10310,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 $753万
@@ -10322,7 +10318,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $755万
@@ -10330,7 +10326,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="E26" s="22" t="inlineStr">
+      <c r="E26" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $857万
@@ -10338,7 +10334,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="F26" s="22" t="inlineStr">
+      <c r="F26" s="23" t="inlineStr">
         <is>
           <t>E | 374呎 (2房)
 $1350万
@@ -10346,7 +10342,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="G26" s="23" t="inlineStr">
+      <c r="G26" s="22" t="inlineStr">
         <is>
           <t>F | 251呎 (1房)
 招标单位

--- a/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
+++ b/web/files/港岛-坚尼地城及摩星岭-海嵎.xlsx
@@ -121,13 +121,13 @@
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
+      <color rgb="00660000"/>
       <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
       <sz val="8"/>
     </font>
   </fonts>
@@ -272,10 +272,10 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1467,23 +1467,19 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t>在售</t>
+          <t>已售</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="inlineStr">
-        <is>
-          <t>招标单位</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="n">
+        <v>22600000</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>47983</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
@@ -1492,12 +1488,12 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>招标单位</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>暂无</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
@@ -1507,7 +1503,7 @@
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
     </row>
@@ -9129,7 +9125,7 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C3" s="15" t="inlineStr">
@@ -9139,7 +9135,7 @@
       </c>
       <c r="D3" s="16" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E3" s="17" t="inlineStr">
@@ -9267,12 +9263,12 @@
       <c r="B7" s="22" t="inlineStr">
         <is>
           <t>A | 471呎 (2房)
-招标单位
--
-(在售)</t>
-        </is>
-      </c>
-      <c r="C7" s="22" t="inlineStr">
+$2260万
+$47,983/呎
+(26年-08月-31日)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 招标单位
@@ -9280,7 +9276,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 招标单位
@@ -9288,7 +9284,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>D | 328呎 (1房)
 招标单位
@@ -9296,7 +9292,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 招标单位
@@ -9312,7 +9308,7 @@
           <t>26</t>
         </is>
       </c>
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $1016万
@@ -9320,7 +9316,7 @@
 (26年-05月-12日)</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $1026万
@@ -9328,7 +9324,7 @@
 (26年-07月-08日)</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $1028万
@@ -9336,7 +9332,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="E8" s="23" t="inlineStr">
+      <c r="E8" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1153万
@@ -9344,7 +9340,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1425万
@@ -9352,7 +9348,7 @@
 (26年-05月-11日)</t>
         </is>
       </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 招标单位
@@ -9367,7 +9363,7 @@
           <t>25</t>
         </is>
       </c>
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $994万
@@ -9375,7 +9371,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $1011万
@@ -9383,7 +9379,7 @@
 (26年-04月-21日)</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $1013万
@@ -9391,7 +9387,7 @@
 (26年-05月-20日)</t>
         </is>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1139万
@@ -9399,7 +9395,7 @@
 (26年-05月-07日)</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1410万
@@ -9407,7 +9403,7 @@
 (26年-05月-04日)</t>
         </is>
       </c>
-      <c r="G9" s="23" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $993万
@@ -9422,7 +9418,7 @@
           <t>23</t>
         </is>
       </c>
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $1031万
@@ -9430,7 +9426,7 @@
 (26年-08月-27日)</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $1042万
@@ -9438,7 +9434,7 @@
 (26年-08月-14日)</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $1045万
@@ -9446,7 +9442,7 @@
 (26年-08月-27日)</t>
         </is>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 招标单位
@@ -9454,7 +9450,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1452万
@@ -9462,7 +9458,7 @@
 (26年-08月-25日)</t>
         </is>
       </c>
-      <c r="G10" s="22" t="inlineStr">
+      <c r="G10" s="23" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 招标单位
@@ -9477,7 +9473,7 @@
           <t>22</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $953万
@@ -9485,7 +9481,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $977万
@@ -9493,7 +9489,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $980万
@@ -9501,7 +9497,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1110万
@@ -9509,7 +9505,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1376万
@@ -9517,7 +9513,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="G11" s="23" t="inlineStr">
+      <c r="G11" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $915万
@@ -9532,7 +9528,7 @@
           <t>21</t>
         </is>
       </c>
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $924万
@@ -9540,7 +9536,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $946万
@@ -9548,7 +9544,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $948万
@@ -9556,7 +9552,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1076万
@@ -9564,7 +9560,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1333万
@@ -9572,7 +9568,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="G12" s="23" t="inlineStr">
+      <c r="G12" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $896万
@@ -9587,7 +9583,7 @@
           <t>20</t>
         </is>
       </c>
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $916万
@@ -9595,7 +9591,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $937万
@@ -9603,7 +9599,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $940万
@@ -9611,7 +9607,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1078万
@@ -9619,7 +9615,7 @@
 (26年-04月-24日)</t>
         </is>
       </c>
-      <c r="F13" s="23" t="inlineStr">
+      <c r="F13" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1322万
@@ -9627,7 +9623,7 @@
 (26年-04月-27日)</t>
         </is>
       </c>
-      <c r="G13" s="23" t="inlineStr">
+      <c r="G13" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $898万
@@ -9642,7 +9638,7 @@
           <t>19</t>
         </is>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $903万
@@ -9650,7 +9646,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $927万
@@ -9658,7 +9654,7 @@
 (26年-04月-13日)</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $929万
@@ -9666,7 +9662,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="E14" s="23" t="inlineStr">
+      <c r="E14" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1056万
@@ -9674,7 +9670,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="F14" s="23" t="inlineStr">
+      <c r="F14" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1307万
@@ -9682,7 +9678,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="G14" s="23" t="inlineStr">
+      <c r="G14" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $868万
@@ -9697,7 +9693,7 @@
           <t>18</t>
         </is>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $898万
@@ -9705,7 +9701,7 @@
 (26年-04月-09日)</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $918万
@@ -9713,7 +9709,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D15" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $920万
@@ -9721,7 +9717,7 @@
 (26年-04月-08日)</t>
         </is>
       </c>
-      <c r="E15" s="23" t="inlineStr">
+      <c r="E15" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1045万
@@ -9729,7 +9725,7 @@
 (26年-04月-14日)</t>
         </is>
       </c>
-      <c r="F15" s="23" t="inlineStr">
+      <c r="F15" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1294万
@@ -9737,7 +9733,7 @@
 (26年-04月-28日)</t>
         </is>
       </c>
-      <c r="G15" s="23" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $860万
@@ -9752,7 +9748,7 @@
           <t>17</t>
         </is>
       </c>
-      <c r="B16" s="23" t="inlineStr">
+      <c r="B16" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $868万
@@ -9760,7 +9756,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="C16" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $888万
@@ -9768,7 +9764,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D16" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $891万
@@ -9776,7 +9772,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="E16" s="23" t="inlineStr">
+      <c r="E16" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $1023万
@@ -9784,7 +9780,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="F16" s="23" t="inlineStr">
+      <c r="F16" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1253万
@@ -9792,7 +9788,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="G16" s="23" t="inlineStr">
+      <c r="G16" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $834万
@@ -9807,7 +9803,7 @@
           <t>16</t>
         </is>
       </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $812万
@@ -9815,7 +9811,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $832万
@@ -9823,7 +9819,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $834万
@@ -9831,7 +9827,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="E17" s="23" t="inlineStr">
+      <c r="E17" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $947万
@@ -9839,7 +9835,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1173万
@@ -9847,7 +9843,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="G17" s="23" t="inlineStr">
+      <c r="G17" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $780万
@@ -9862,7 +9858,7 @@
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $804万
@@ -9870,7 +9866,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $823万
@@ -9878,7 +9874,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $824万
@@ -9886,7 +9882,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="E18" s="23" t="inlineStr">
+      <c r="E18" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $936万
@@ -9894,7 +9890,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="F18" s="23" t="inlineStr">
+      <c r="F18" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1160万
@@ -9902,7 +9898,7 @@
 (26年-04月-02日)</t>
         </is>
       </c>
-      <c r="G18" s="23" t="inlineStr">
+      <c r="G18" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $772万
@@ -9917,7 +9913,7 @@
           <t>12</t>
         </is>
       </c>
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $821万
@@ -9925,7 +9921,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $843万
@@ -9933,7 +9929,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $845万
@@ -9941,7 +9937,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="E19" s="23" t="inlineStr">
+      <c r="E19" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $956万
@@ -9949,7 +9945,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F19" s="23" t="inlineStr">
+      <c r="F19" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1184万
@@ -9957,7 +9953,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="G19" s="23" t="inlineStr">
+      <c r="G19" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $788万
@@ -9972,7 +9968,7 @@
           <t>11</t>
         </is>
       </c>
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $786万
@@ -9980,7 +9976,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $805万
@@ -9988,7 +9984,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $807万
@@ -9996,7 +9992,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="E20" s="23" t="inlineStr">
+      <c r="E20" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $916万
@@ -10004,7 +10000,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F20" s="23" t="inlineStr">
+      <c r="F20" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1135万
@@ -10012,7 +10008,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="G20" s="23" t="inlineStr">
+      <c r="G20" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $755万
@@ -10027,7 +10023,7 @@
           <t>10</t>
         </is>
       </c>
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $778万
@@ -10035,7 +10031,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $797万
@@ -10043,7 +10039,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $798万
@@ -10051,7 +10047,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="E21" s="23" t="inlineStr">
+      <c r="E21" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $907万
@@ -10059,7 +10055,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F21" s="23" t="inlineStr">
+      <c r="F21" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1123万
@@ -10067,7 +10063,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="G21" s="23" t="inlineStr">
+      <c r="G21" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $748万
@@ -10082,7 +10078,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $769万
@@ -10090,7 +10086,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $788万
@@ -10098,7 +10094,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $789万
@@ -10106,7 +10102,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="E22" s="23" t="inlineStr">
+      <c r="E22" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $896万
@@ -10114,7 +10110,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="F22" s="23" t="inlineStr">
+      <c r="F22" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1110万
@@ -10122,7 +10118,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="G22" s="23" t="inlineStr">
+      <c r="G22" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $739万
@@ -10137,7 +10133,7 @@
           <t>8</t>
         </is>
       </c>
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $761万
@@ -10145,7 +10141,7 @@
 (26年-03月-26日)</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $779万
@@ -10153,7 +10149,7 @@
 (26年-03月-27日)</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $781万
@@ -10161,7 +10157,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="E23" s="23" t="inlineStr">
+      <c r="E23" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $887万
@@ -10169,7 +10165,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="F23" s="23" t="inlineStr">
+      <c r="F23" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1098万
@@ -10177,7 +10173,7 @@
 (26年-03月-30日)</t>
         </is>
       </c>
-      <c r="G23" s="23" t="inlineStr">
+      <c r="G23" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $731万
@@ -10192,7 +10188,7 @@
           <t>7</t>
         </is>
       </c>
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $752万
@@ -10200,7 +10196,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $770万
@@ -10208,7 +10204,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $772万
@@ -10216,7 +10212,7 @@
 (26年-03月-24日)</t>
         </is>
       </c>
-      <c r="E24" s="23" t="inlineStr">
+      <c r="E24" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $876万
@@ -10224,7 +10220,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="F24" s="23" t="inlineStr">
+      <c r="F24" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1085万
@@ -10232,7 +10228,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="G24" s="23" t="inlineStr">
+      <c r="G24" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $722万
@@ -10247,7 +10243,7 @@
           <t>6</t>
         </is>
       </c>
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="22" t="inlineStr">
         <is>
           <t>A | 287呎 (1房)
 $744万
@@ -10255,7 +10251,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="22" t="inlineStr">
         <is>
           <t>B | 284呎 (1房)
 $762万
@@ -10263,7 +10259,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $763万
@@ -10271,7 +10267,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="E25" s="23" t="inlineStr">
+      <c r="E25" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $867万
@@ -10279,7 +10275,7 @@
 (26年-03月-25日)</t>
         </is>
       </c>
-      <c r="F25" s="23" t="inlineStr">
+      <c r="F25" s="22" t="inlineStr">
         <is>
           <t>E | 412呎 (2房)
 $1074万
@@ -10287,7 +10283,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="G25" s="23" t="inlineStr">
+      <c r="G25" s="22" t="inlineStr">
         <is>
           <t>F | 288呎 (1房)
 $715万
@@ -10302,7 +10298,7 @@
           <t>5</t>
         </is>
       </c>
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>A | 247呎 (1房)
 招标单位
@@ -10310,7 +10306,7 @@
 (在售)</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="22" t="inlineStr">
         <is>
           <t>B | 286呎 (1房)
 $753万
@@ -10318,7 +10314,7 @@
 (26年-03月-20日)</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="22" t="inlineStr">
         <is>
           <t>C | 284呎 (1房)
 $755万
@@ -10326,7 +10322,7 @@
 (26年-04月-01日)</t>
         </is>
       </c>
-      <c r="E26" s="23" t="inlineStr">
+      <c r="E26" s="22" t="inlineStr">
         <is>
           <t>D | 325呎 (1房)
 $857万
@@ -10334,7 +10330,7 @@
 (26年-03月-31日)</t>
         </is>
       </c>
-      <c r="F26" s="23" t="inlineStr">
+      <c r="F26" s="22" t="inlineStr">
         <is>
           <t>E | 374呎 (2房)
 $1350万
@@ -10342,7 +10338,7 @@
 (26年-04月-15日)</t>
         </is>
       </c>
-      <c r="G26" s="22" t="inlineStr">
+      <c r="G26" s="23" t="inlineStr">
         <is>
           <t>F | 251呎 (1房)
 招标单位
